--- a/output/roomself_excel/12137.xlsx
+++ b/output/roomself_excel/12137.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>412880</v>
+        <v>104890</v>
       </c>
       <c r="D2" t="n">
-        <v>7952</v>
+        <v>2600</v>
       </c>
       <c r="E2" t="n">
-        <v>788</v>
+        <v>365</v>
       </c>
       <c r="F2" t="n">
-        <v>782</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>165110</v>
+        <v>203853</v>
       </c>
       <c r="D3" t="n">
-        <v>3252</v>
+        <v>3664</v>
       </c>
       <c r="E3" t="n">
-        <v>596</v>
+        <v>529</v>
       </c>
       <c r="F3" t="n">
-        <v>443</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>103056</v>
+        <v>13608</v>
       </c>
       <c r="D4" t="n">
-        <v>2572</v>
+        <v>936</v>
       </c>
       <c r="E4" t="n">
-        <v>339</v>
+        <v>126</v>
       </c>
       <c r="F4" t="n">
-        <v>339</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>77218</v>
+        <v>104137</v>
       </c>
       <c r="D5" t="n">
-        <v>3248</v>
+        <v>3404</v>
       </c>
       <c r="E5" t="n">
-        <v>253</v>
+        <v>307</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>122845</v>
+        <v>17064</v>
       </c>
       <c r="D6" t="n">
-        <v>2824</v>
+        <v>1064</v>
       </c>
       <c r="E6" t="n">
-        <v>414</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>331</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38752</v>
+        <v>36608</v>
       </c>
       <c r="D7" t="n">
-        <v>1588</v>
+        <v>1536</v>
       </c>
       <c r="E7" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F7" t="n">
-        <v>193</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>46816</v>
+        <v>165110</v>
       </c>
       <c r="D8" t="n">
-        <v>1732</v>
+        <v>3252</v>
       </c>
       <c r="E8" t="n">
-        <v>584</v>
+        <v>443</v>
       </c>
       <c r="F8" t="n">
-        <v>137</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42130</v>
+        <v>103056</v>
       </c>
       <c r="D9" t="n">
-        <v>1696</v>
+        <v>2572</v>
       </c>
       <c r="E9" t="n">
-        <v>202</v>
+        <v>339</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17064</v>
+        <v>77218</v>
       </c>
       <c r="D10" t="n">
-        <v>1064</v>
+        <v>3248</v>
       </c>
       <c r="E10" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18084</v>
+        <v>122845</v>
       </c>
       <c r="D11" t="n">
-        <v>1132</v>
+        <v>2824</v>
       </c>
       <c r="E11" t="n">
-        <v>108</v>
+        <v>414</v>
       </c>
       <c r="F11" t="n">
-        <v>54</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13608</v>
+        <v>38752</v>
       </c>
       <c r="D12" t="n">
-        <v>936</v>
+        <v>1588</v>
       </c>
       <c r="E12" t="n">
-        <v>126</v>
+        <v>243</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,64 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36608</v>
+        <v>46816</v>
       </c>
       <c r="D13" t="n">
-        <v>1536</v>
+        <v>1732</v>
       </c>
       <c r="E13" t="n">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="F13" t="n">
-        <v>176</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>42130</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1696</v>
+      </c>
+      <c r="E14" t="n">
+        <v>202</v>
+      </c>
+      <c r="F14" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>18084</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1132</v>
+      </c>
+      <c r="E15" t="n">
+        <v>108</v>
+      </c>
+      <c r="F15" t="n">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/12137.xlsx
+++ b/output/roomself_excel/12137.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2600</v>
       </c>
-      <c r="E2" t="n">
-        <v>365</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>327</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>305</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>3664</v>
       </c>
-      <c r="E3" t="n">
-        <v>529</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>423</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>507</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,23 @@
       <c r="D4" t="n">
         <v>936</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>126</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>20</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +625,23 @@
       <c r="D5" t="n">
         <v>3404</v>
       </c>
-      <c r="E5" t="n">
-        <v>307</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
+        <v>301</v>
+      </c>
+      <c r="G5" t="n">
         <v>20</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +658,23 @@
       <c r="D6" t="n">
         <v>1064</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>124</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>19</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +691,38 @@
       <c r="D7" t="n">
         <v>1536</v>
       </c>
-      <c r="E7" t="n">
-        <v>240</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>176</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>176</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>208</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +740,31 @@
       <c r="D8" t="n">
         <v>3252</v>
       </c>
-      <c r="E8" t="n">
-        <v>443</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>414</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>418</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +781,38 @@
       <c r="D9" t="n">
         <v>2572</v>
       </c>
-      <c r="E9" t="n">
-        <v>339</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>339</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>304</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +830,23 @@
       <c r="D10" t="n">
         <v>3248</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="G10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +863,31 @@
       <c r="D11" t="n">
         <v>2824</v>
       </c>
-      <c r="E11" t="n">
-        <v>414</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>331</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>395</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +904,31 @@
       <c r="D12" t="n">
         <v>1588</v>
       </c>
-      <c r="E12" t="n">
-        <v>243</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>193</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>173</v>
+      </c>
+      <c r="J12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +945,23 @@
       <c r="D13" t="n">
         <v>1732</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>209</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>19</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +978,31 @@
       <c r="D14" t="n">
         <v>1696</v>
       </c>
-      <c r="E14" t="n">
-        <v>202</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="G14" t="n">
+        <v>19</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>143</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1019,23 @@
       <c r="D15" t="n">
         <v>1132</v>
       </c>
-      <c r="E15" t="n">
-        <v>108</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
